--- a/data/trans_dic/IP1015-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1015-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen parálisis</t>
+          <t>Menores que padecen parálisis (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,33</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,0; 0,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,17 +1008,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1027,27 +1028,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,2</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,89</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,17</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,06</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,27</t>
         </is>
       </c>
     </row>
@@ -1117,17 +1118,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,34</t>
+          <t>0,0; 0,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1137,27 +1138,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,73</t>
+          <t>0,08; 0,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,4</t>
+          <t>0,05; 0,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,44</t>
+          <t>0,05; 0,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,34</t>
+          <t>0,0; 0,33</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen parálisis (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3219</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3452</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3150</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3798</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2414</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2595</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3347</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3057</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4887</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3743</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5370</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5011</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3727</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4823</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2074</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2074</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2521</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2169</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>673; 5550</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>606; 5701</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4223</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>672; 6233</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>685; 6167</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4769</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1015-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1015-Habitat-trans_dic.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,61</t>
+          <t>0,0; 0,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1023,32 +1023,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,31</t>
+          <t>0,0; 0,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1133,32 +1133,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,77</t>
+          <t>0,09; 0,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,76</t>
+          <t>0,08; 0,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,44</t>
+          <t>0,0; 0,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,42</t>
+          <t>0,05; 0,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,33</t>
+          <t>0,0; 0,29</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3219</t>
+          <t>0; 3400</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3452</t>
+          <t>0; 4101</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3150</t>
+          <t>0; 3205</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3798</t>
+          <t>0; 4047</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2414</t>
+          <t>0; 2416</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2595</t>
+          <t>0; 2314</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3347</t>
+          <t>0; 3074</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3057</t>
+          <t>0; 3043</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1921,32 +1921,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4887</t>
+          <t>0; 4913</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3743</t>
+          <t>0; 3789</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5370</t>
+          <t>0; 4703</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5011</t>
+          <t>0; 4884</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3727</t>
+          <t>0; 3740</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4823</t>
+          <t>0; 4688</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2169</t>
+          <t>0; 2397</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2084,32 +2084,32 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>673; 5550</t>
+          <t>674; 5775</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>606; 5701</t>
+          <t>604; 5543</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4223</t>
+          <t>0; 4777</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>672; 6233</t>
+          <t>0; 5532</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>685; 6167</t>
+          <t>687; 6259</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4769</t>
+          <t>0; 4180</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1015-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1015-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,12 +625,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -740,22 +740,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0,23%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,54</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,32 +1008,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>0,07%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,09; 0,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>0,08; 0,73</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,65</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,34</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 0,8</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,08; 0,74</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,39</t>
+          <t>0,05; 0,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,43</t>
+          <t>0,05; 0,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,29</t>
+          <t>0,0; 0,34</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1364,12 +1364,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>687</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4269</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3509</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3400</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4101</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3205</t>
+          <t>0; 3705</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4047</t>
+          <t>0; 3855</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1479,22 +1479,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1532,22 +1532,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>480</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2416</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2615</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2314</t>
+          <t>0; 2417</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>607</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2466</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3074</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3043</t>
+          <t>0; 3229</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4894</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3451</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4874</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4913</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3789</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4703</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4884</t>
+          <t>0; 4899</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3740</t>
+          <t>0; 4416</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4688</t>
+          <t>0; 5235</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2074</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2041</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>672; 5534</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2397</t>
+          <t>607; 5434</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4836</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>674; 5775</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>604; 5543</t>
+          <t>0; 2419</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4777</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5532</t>
+          <t>672; 5560</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>687; 6259</t>
+          <t>683; 6410</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4180</t>
+          <t>0; 4926</t>
         </is>
       </c>
     </row>
